--- a/Results_experiment/exp_5/preds_3364444555550000.xlsx
+++ b/Results_experiment/exp_5/preds_3364444555550000.xlsx
@@ -1443,7 +1443,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D2">
-        <v>1.565927743911743</v>
+        <v>1.331524968147278</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1457,7 +1457,7 @@
         <v>12.30000019073486</v>
       </c>
       <c r="D3">
-        <v>9.258257865905762</v>
+        <v>9.602741241455078</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1471,7 +1471,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D4">
-        <v>1.705631732940674</v>
+        <v>1.709387302398682</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1485,7 +1485,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D5">
-        <v>2.825540065765381</v>
+        <v>3.486703395843506</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1499,7 +1499,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D6">
-        <v>2.324003934860229</v>
+        <v>2.602629899978638</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1513,7 +1513,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D7">
-        <v>2.683268070220947</v>
+        <v>3.081475257873535</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1527,7 +1527,7 @@
         <v>18</v>
       </c>
       <c r="D8">
-        <v>3.317569494247437</v>
+        <v>3.309375286102295</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1541,7 +1541,7 @@
         <v>33.70000076293945</v>
       </c>
       <c r="D9">
-        <v>20.21743392944336</v>
+        <v>20.27160453796387</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1555,7 +1555,7 @@
         <v>24.39999961853027</v>
       </c>
       <c r="D10">
-        <v>12.46077728271484</v>
+        <v>13.41717910766602</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1569,7 +1569,7 @@
         <v>12</v>
       </c>
       <c r="D11">
-        <v>6.98117733001709</v>
+        <v>6.928945541381836</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1583,7 +1583,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D12">
-        <v>6.824329376220703</v>
+        <v>6.578042030334473</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1597,7 +1597,7 @@
         <v>19.60000038146973</v>
       </c>
       <c r="D13">
-        <v>18.75503349304199</v>
+        <v>17.20002555847168</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1611,7 +1611,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D14">
-        <v>1.696459770202637</v>
+        <v>1.513374209403992</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1625,7 +1625,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D15">
-        <v>1.358910083770752</v>
+        <v>1.126213431358337</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1639,7 +1639,7 @@
         <v>20.60000038146973</v>
       </c>
       <c r="D16">
-        <v>2.365627288818359</v>
+        <v>4.300208568572998</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1653,7 +1653,7 @@
         <v>9.5</v>
       </c>
       <c r="D17">
-        <v>7.884870529174805</v>
+        <v>7.325705528259277</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1667,7 +1667,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D18">
-        <v>17.30629348754883</v>
+        <v>17.0691089630127</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1681,7 +1681,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D19">
-        <v>1.339480876922607</v>
+        <v>1.129294872283936</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1695,7 +1695,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D20">
-        <v>6.822036743164062</v>
+        <v>7.168551921844482</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1709,7 +1709,7 @@
         <v>14</v>
       </c>
       <c r="D21">
-        <v>11.86740589141846</v>
+        <v>9.58256721496582</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1723,7 +1723,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D22">
-        <v>2.899549722671509</v>
+        <v>2.153400897979736</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1737,7 +1737,7 @@
         <v>12.39999961853027</v>
       </c>
       <c r="D23">
-        <v>8.633520126342773</v>
+        <v>8.769275665283203</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1751,7 +1751,7 @@
         <v>13.69999980926514</v>
       </c>
       <c r="D24">
-        <v>7.236098289489746</v>
+        <v>7.13503885269165</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1765,7 +1765,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D25">
-        <v>3.317366123199463</v>
+        <v>3.56762170791626</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1779,7 +1779,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D26">
-        <v>4.821546077728271</v>
+        <v>4.356405735015869</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1793,7 +1793,7 @@
         <v>3</v>
       </c>
       <c r="D27">
-        <v>7.03101921081543</v>
+        <v>5.830560684204102</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1807,7 +1807,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D28">
-        <v>3.776830196380615</v>
+        <v>3.836545467376709</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1821,7 +1821,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D29">
-        <v>3.028550148010254</v>
+        <v>3.483907222747803</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1835,7 +1835,7 @@
         <v>18.79999923706055</v>
       </c>
       <c r="D30">
-        <v>7.222963333129883</v>
+        <v>7.048048496246338</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1849,7 +1849,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D31">
-        <v>1.512733817100525</v>
+        <v>1.764395475387573</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1863,7 +1863,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D32">
-        <v>3.391342878341675</v>
+        <v>4.056212902069092</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1877,7 +1877,7 @@
         <v>23.10000038146973</v>
       </c>
       <c r="D33">
-        <v>21.21187210083008</v>
+        <v>19.23567008972168</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1891,7 +1891,7 @@
         <v>19.39999961853027</v>
       </c>
       <c r="D34">
-        <v>20.79691314697266</v>
+        <v>20.01993751525879</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1905,7 +1905,7 @@
         <v>9.5</v>
       </c>
       <c r="D35">
-        <v>2.953461647033691</v>
+        <v>1.994715571403503</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1919,7 +1919,7 @@
         <v>1.5</v>
       </c>
       <c r="D36">
-        <v>1.354125022888184</v>
+        <v>3.985166072845459</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1933,7 +1933,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D37">
-        <v>4.116132736206055</v>
+        <v>3.374310493469238</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1947,7 +1947,7 @@
         <v>5.5</v>
       </c>
       <c r="D38">
-        <v>5.21835994720459</v>
+        <v>2.509906768798828</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1961,7 +1961,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D39">
-        <v>8.24676513671875</v>
+        <v>4.621617317199707</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1975,7 +1975,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D40">
-        <v>3.777380704879761</v>
+        <v>2.54065990447998</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1989,7 +1989,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D41">
-        <v>3.170930147171021</v>
+        <v>3.270796298980713</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2003,7 +2003,7 @@
         <v>16.70000076293945</v>
       </c>
       <c r="D42">
-        <v>11.4076099395752</v>
+        <v>11.36429595947266</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2017,7 +2017,7 @@
         <v>3.5</v>
       </c>
       <c r="D43">
-        <v>2.818371295928955</v>
+        <v>2.885948181152344</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2031,7 +2031,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D44">
-        <v>7.082408905029297</v>
+        <v>7.066936016082764</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2045,7 +2045,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D45">
-        <v>8.563636779785156</v>
+        <v>9.812464714050293</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2059,7 +2059,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D46">
-        <v>1.810335874557495</v>
+        <v>2.036321640014648</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2073,7 +2073,7 @@
         <v>3.5</v>
       </c>
       <c r="D47">
-        <v>1.369835734367371</v>
+        <v>1.758223414421082</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2087,7 +2087,7 @@
         <v>12.19999980926514</v>
       </c>
       <c r="D48">
-        <v>3.945134401321411</v>
+        <v>4.102538108825684</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2101,7 +2101,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D49">
-        <v>3.156734943389893</v>
+        <v>3.755903244018555</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2115,7 +2115,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D50">
-        <v>2.642471551895142</v>
+        <v>1.411520719528198</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2129,7 +2129,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D51">
-        <v>3.985224485397339</v>
+        <v>3.916591167449951</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2143,7 +2143,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D52">
-        <v>2.727488040924072</v>
+        <v>2.64563775062561</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2157,7 +2157,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D53">
-        <v>2.065602540969849</v>
+        <v>2.981132030487061</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2171,7 +2171,7 @@
         <v>13.30000019073486</v>
       </c>
       <c r="D54">
-        <v>9.588687896728516</v>
+        <v>9.813720703125</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2185,7 +2185,7 @@
         <v>3.5</v>
       </c>
       <c r="D55">
-        <v>3.828963279724121</v>
+        <v>3.889853477478027</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2199,7 +2199,7 @@
         <v>20.20000076293945</v>
       </c>
       <c r="D56">
-        <v>18.93030548095703</v>
+        <v>16.67787170410156</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2213,7 +2213,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D57">
-        <v>1.500258564949036</v>
+        <v>1.649700045585632</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2227,7 +2227,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D58">
-        <v>6.975249290466309</v>
+        <v>7.620621681213379</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2241,7 +2241,7 @@
         <v>29.79999923706055</v>
       </c>
       <c r="D59">
-        <v>16.18238830566406</v>
+        <v>16.4629077911377</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2255,7 +2255,7 @@
         <v>13.19999980926514</v>
       </c>
       <c r="D60">
-        <v>4.072722434997559</v>
+        <v>5.637042045593262</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2269,7 +2269,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D61">
-        <v>8.820222854614258</v>
+        <v>7.538212299346924</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2283,7 +2283,7 @@
         <v>16.10000038146973</v>
       </c>
       <c r="D62">
-        <v>6.054745674133301</v>
+        <v>6.601480007171631</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2297,7 +2297,7 @@
         <v>1</v>
       </c>
       <c r="D63">
-        <v>2.599740266799927</v>
+        <v>1.967383146286011</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2311,7 +2311,7 @@
         <v>17.39999961853027</v>
       </c>
       <c r="D64">
-        <v>7.618683815002441</v>
+        <v>10.3299674987793</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2325,7 +2325,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D65">
-        <v>1.655470609664917</v>
+        <v>1.33985424041748</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2339,7 +2339,7 @@
         <v>14.80000019073486</v>
       </c>
       <c r="D66">
-        <v>9.187883377075195</v>
+        <v>9.829790115356445</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2353,7 +2353,7 @@
         <v>5</v>
       </c>
       <c r="D67">
-        <v>2.046109914779663</v>
+        <v>2.82429027557373</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2367,7 +2367,7 @@
         <v>19.79999923706055</v>
       </c>
       <c r="D68">
-        <v>18.46915054321289</v>
+        <v>17.69890403747559</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2381,7 +2381,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D69">
-        <v>1.481504440307617</v>
+        <v>1.332973480224609</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2395,7 +2395,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D70">
-        <v>3.231164693832397</v>
+        <v>2.760818719863892</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2409,7 +2409,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D71">
-        <v>2.361796617507935</v>
+        <v>3.820317268371582</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2423,7 +2423,7 @@
         <v>9.300000190734863</v>
       </c>
       <c r="D72">
-        <v>4.45832347869873</v>
+        <v>8.235433578491211</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2437,7 +2437,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D73">
-        <v>3.851138830184937</v>
+        <v>3.795211791992188</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2451,7 +2451,7 @@
         <v>15.30000019073486</v>
       </c>
       <c r="D74">
-        <v>6.65871524810791</v>
+        <v>8.472168922424316</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2465,7 +2465,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D75">
-        <v>5.868163108825684</v>
+        <v>4.851030826568604</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2479,7 +2479,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D76">
-        <v>2.378903388977051</v>
+        <v>2.751911640167236</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2493,7 +2493,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D77">
-        <v>1.81696891784668</v>
+        <v>2.072529792785645</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2507,7 +2507,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D78">
-        <v>6.342026710510254</v>
+        <v>4.664156436920166</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2521,7 +2521,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D79">
-        <v>1.36444628238678</v>
+        <v>1.125128388404846</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2535,7 +2535,7 @@
         <v>11.30000019073486</v>
       </c>
       <c r="D80">
-        <v>8.973323822021484</v>
+        <v>9.24910831451416</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2549,7 +2549,7 @@
         <v>21.29999923706055</v>
       </c>
       <c r="D81">
-        <v>6.732159614562988</v>
+        <v>5.732287883758545</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2563,7 +2563,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D82">
-        <v>7.02071475982666</v>
+        <v>6.551433086395264</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2577,7 +2577,7 @@
         <v>10.39999961853027</v>
       </c>
       <c r="D83">
-        <v>8.013994216918945</v>
+        <v>7.194221019744873</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2591,7 +2591,7 @@
         <v>20.39999961853027</v>
       </c>
       <c r="D84">
-        <v>17.54349136352539</v>
+        <v>16.88052177429199</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2605,7 +2605,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D85">
-        <v>1.367183923721313</v>
+        <v>1.128923177719116</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2619,7 +2619,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D86">
-        <v>3.792736768722534</v>
+        <v>5.871527194976807</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2633,7 +2633,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D87">
-        <v>2.624506711959839</v>
+        <v>2.64068865776062</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2647,7 +2647,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D88">
-        <v>5.144462585449219</v>
+        <v>4.564015865325928</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2661,7 +2661,7 @@
         <v>11.69999980926514</v>
       </c>
       <c r="D89">
-        <v>12.81415748596191</v>
+        <v>11.52118492126465</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2675,7 +2675,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D90">
-        <v>3.912477731704712</v>
+        <v>5.774683475494385</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2689,7 +2689,7 @@
         <v>13.69999980926514</v>
       </c>
       <c r="D91">
-        <v>6.636204719543457</v>
+        <v>4.603691101074219</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2703,7 +2703,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D92">
-        <v>6.743448257446289</v>
+        <v>7.435980796813965</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2717,7 +2717,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D93">
-        <v>3.836552858352661</v>
+        <v>4.022399425506592</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2731,7 +2731,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D94">
-        <v>3.468918085098267</v>
+        <v>3.920174121856689</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2745,7 +2745,7 @@
         <v>5.5</v>
       </c>
       <c r="D95">
-        <v>3.556734800338745</v>
+        <v>3.990477561950684</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2759,7 +2759,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D96">
-        <v>1.595431566238403</v>
+        <v>2.186623096466064</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2773,7 +2773,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>3.548169374465942</v>
+        <v>3.796347141265869</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2787,7 +2787,7 @@
         <v>6</v>
       </c>
       <c r="D98">
-        <v>3.470995664596558</v>
+        <v>3.832239151000977</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2801,7 +2801,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D99">
-        <v>2.339160919189453</v>
+        <v>2.750118732452393</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2815,7 +2815,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D100">
-        <v>6.064779281616211</v>
+        <v>6.542614936828613</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2829,7 +2829,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D101">
-        <v>2.762991189956665</v>
+        <v>2.892777442932129</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2843,7 +2843,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D102">
-        <v>3.327676296234131</v>
+        <v>3.033924579620361</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2857,7 +2857,7 @@
         <v>21.89999961853027</v>
       </c>
       <c r="D103">
-        <v>15.03470420837402</v>
+        <v>14.2797908782959</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2871,7 +2871,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D104">
-        <v>3.13958215713501</v>
+        <v>3.680867671966553</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2885,7 +2885,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D105">
-        <v>1.284197330474854</v>
+        <v>1.234443187713623</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2899,7 +2899,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D106">
-        <v>2.901040554046631</v>
+        <v>2.26223087310791</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2913,7 +2913,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D107">
-        <v>1.346774935722351</v>
+        <v>1.095995664596558</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2927,7 +2927,7 @@
         <v>19</v>
       </c>
       <c r="D108">
-        <v>19.02531051635742</v>
+        <v>17.4621410369873</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2941,7 +2941,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D109">
-        <v>2.326645374298096</v>
+        <v>2.686724662780762</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2955,7 +2955,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D110">
-        <v>6.103565216064453</v>
+        <v>7.150574207305908</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2969,7 +2969,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D111">
-        <v>4.238327980041504</v>
+        <v>3.207473278045654</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2983,7 +2983,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D112">
-        <v>3.617914915084839</v>
+        <v>3.721189975738525</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2997,7 +2997,7 @@
         <v>1.5</v>
       </c>
       <c r="D113">
-        <v>3.86546778678894</v>
+        <v>2.564126968383789</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3011,7 +3011,7 @@
         <v>4</v>
       </c>
       <c r="D114">
-        <v>3.721878290176392</v>
+        <v>3.617341995239258</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3025,7 +3025,7 @@
         <v>11.60000038146973</v>
       </c>
       <c r="D115">
-        <v>3.345334768295288</v>
+        <v>3.910193920135498</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3039,7 +3039,7 @@
         <v>13.5</v>
       </c>
       <c r="D116">
-        <v>9.119033813476562</v>
+        <v>9.033834457397461</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3053,7 +3053,7 @@
         <v>14</v>
       </c>
       <c r="D117">
-        <v>6.453773498535156</v>
+        <v>8.485597610473633</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3067,7 +3067,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="D118">
-        <v>3.939832210540771</v>
+        <v>3.172511100769043</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3081,7 +3081,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D119">
-        <v>3.633507013320923</v>
+        <v>3.988633155822754</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3095,7 +3095,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D120">
-        <v>1.954097032546997</v>
+        <v>1.316088676452637</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3109,7 +3109,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D121">
-        <v>2.965855121612549</v>
+        <v>3.692593097686768</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3123,7 +3123,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D122">
-        <v>4.928680419921875</v>
+        <v>5.74391508102417</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3137,7 +3137,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D123">
-        <v>1.477425336837769</v>
+        <v>1.376769304275513</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3151,7 +3151,7 @@
         <v>17.39999961853027</v>
       </c>
       <c r="D124">
-        <v>15.05930805206299</v>
+        <v>15.81168746948242</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3165,7 +3165,7 @@
         <v>10.60000038146973</v>
       </c>
       <c r="D125">
-        <v>11.81285095214844</v>
+        <v>10.48313140869141</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3179,7 +3179,7 @@
         <v>14.89999961853027</v>
       </c>
       <c r="D126">
-        <v>14.76254367828369</v>
+        <v>15.82489204406738</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3193,7 +3193,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D127">
-        <v>2.97711181640625</v>
+        <v>3.773464202880859</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3207,7 +3207,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D128">
-        <v>3.418800115585327</v>
+        <v>3.53496789932251</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3221,7 +3221,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D129">
-        <v>1.330311894416809</v>
+        <v>1.117579460144043</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3235,7 +3235,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D130">
-        <v>2.969244480133057</v>
+        <v>3.297965049743652</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3249,7 +3249,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D131">
-        <v>2.287748575210571</v>
+        <v>1.608793139457703</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3263,7 +3263,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D132">
-        <v>6.749619483947754</v>
+        <v>7.079400062561035</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3277,7 +3277,7 @@
         <v>19.70000076293945</v>
       </c>
       <c r="D133">
-        <v>16.80105209350586</v>
+        <v>16.97721862792969</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3291,7 +3291,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D134">
-        <v>2.269109964370728</v>
+        <v>3.089196681976318</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3305,7 +3305,7 @@
         <v>10</v>
       </c>
       <c r="D135">
-        <v>4.792773246765137</v>
+        <v>3.240546226501465</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3319,7 +3319,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D136">
-        <v>1.344159960746765</v>
+        <v>1.152551651000977</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3333,7 +3333,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D137">
-        <v>2.640852689743042</v>
+        <v>2.630797863006592</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3347,7 +3347,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D138">
-        <v>3.879816293716431</v>
+        <v>3.891314029693604</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3361,7 +3361,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D139">
-        <v>2.545226573944092</v>
+        <v>2.701184272766113</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3375,7 +3375,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D140">
-        <v>2.298843622207642</v>
+        <v>4.378437042236328</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3389,7 +3389,7 @@
         <v>12.89999961853027</v>
       </c>
       <c r="D141">
-        <v>5.044970512390137</v>
+        <v>4.380496978759766</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3403,7 +3403,7 @@
         <v>21.20000076293945</v>
       </c>
       <c r="D142">
-        <v>12.51771926879883</v>
+        <v>16.14237594604492</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3417,7 +3417,7 @@
         <v>2.5</v>
       </c>
       <c r="D143">
-        <v>1.330366969108582</v>
+        <v>1.116794109344482</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3431,7 +3431,7 @@
         <v>25.89999961853027</v>
       </c>
       <c r="D144">
-        <v>9.202659606933594</v>
+        <v>5.857576370239258</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3445,7 +3445,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D145">
-        <v>3.861406564712524</v>
+        <v>3.660528659820557</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3459,7 +3459,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D146">
-        <v>4.274251937866211</v>
+        <v>4.68378734588623</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3473,7 +3473,7 @@
         <v>19.29999923706055</v>
       </c>
       <c r="D147">
-        <v>7.095162391662598</v>
+        <v>7.167561054229736</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3487,7 +3487,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D148">
-        <v>6.843978881835938</v>
+        <v>4.538046360015869</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3501,7 +3501,7 @@
         <v>10</v>
       </c>
       <c r="D149">
-        <v>6.927644729614258</v>
+        <v>6.799153804779053</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3515,7 +3515,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D150">
-        <v>6.769429206848145</v>
+        <v>7.519055366516113</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3529,7 +3529,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D151">
-        <v>3.58338451385498</v>
+        <v>3.990349292755127</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3543,7 +3543,7 @@
         <v>4.5</v>
       </c>
       <c r="D152">
-        <v>3.994475603103638</v>
+        <v>4.378754138946533</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3557,7 +3557,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D153">
-        <v>2.024817943572998</v>
+        <v>2.872626543045044</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3571,7 +3571,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D154">
-        <v>2.405304670333862</v>
+        <v>2.226330757141113</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3585,7 +3585,7 @@
         <v>9</v>
       </c>
       <c r="D155">
-        <v>2.588845252990723</v>
+        <v>2.640123844146729</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3599,7 +3599,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D156">
-        <v>4.332239151000977</v>
+        <v>3.400716781616211</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3613,7 +3613,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D157">
-        <v>7.017842292785645</v>
+        <v>6.757645606994629</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3627,7 +3627,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D158">
-        <v>16.90728950500488</v>
+        <v>17.88080596923828</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3641,7 +3641,7 @@
         <v>30.79999923706055</v>
       </c>
       <c r="D159">
-        <v>22.53752517700195</v>
+        <v>15.82644271850586</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3655,7 +3655,7 @@
         <v>11.5</v>
       </c>
       <c r="D160">
-        <v>6.948222160339355</v>
+        <v>8.119951248168945</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3669,7 +3669,7 @@
         <v>21.60000038146973</v>
       </c>
       <c r="D161">
-        <v>19.52580451965332</v>
+        <v>19.22643280029297</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3683,7 +3683,7 @@
         <v>14.60000038146973</v>
       </c>
       <c r="D162">
-        <v>12.27931022644043</v>
+        <v>11.0004711151123</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3697,7 +3697,7 @@
         <v>2.5</v>
       </c>
       <c r="D163">
-        <v>2.836991310119629</v>
+        <v>3.050530433654785</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3711,7 +3711,7 @@
         <v>2</v>
       </c>
       <c r="D164">
-        <v>3.537250757217407</v>
+        <v>4.179604053497314</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3725,7 +3725,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D165">
-        <v>2.295881748199463</v>
+        <v>2.047847270965576</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3739,7 +3739,7 @@
         <v>12.39999961853027</v>
       </c>
       <c r="D166">
-        <v>19.83270645141602</v>
+        <v>19.58589363098145</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3753,7 +3753,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D167">
-        <v>1.496266603469849</v>
+        <v>2.026256084442139</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3767,7 +3767,7 @@
         <v>2</v>
       </c>
       <c r="D168">
-        <v>3.674165010452271</v>
+        <v>3.794572830200195</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3781,7 +3781,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D169">
-        <v>7.809344291687012</v>
+        <v>7.389082431793213</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3795,7 +3795,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D170">
-        <v>1.695081472396851</v>
+        <v>1.47122049331665</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3809,7 +3809,7 @@
         <v>5</v>
       </c>
       <c r="D171">
-        <v>1.877477526664734</v>
+        <v>1.925689578056335</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3823,7 +3823,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D172">
-        <v>1.476559400558472</v>
+        <v>2.046817064285278</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -3837,7 +3837,7 @@
         <v>14.10000038146973</v>
       </c>
       <c r="D173">
-        <v>8.922103881835938</v>
+        <v>9.68449592590332</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -3851,7 +3851,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D174">
-        <v>7.31244945526123</v>
+        <v>8.868094444274902</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -3865,7 +3865,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D175">
-        <v>10.62830924987793</v>
+        <v>10.56396389007568</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -3879,7 +3879,7 @@
         <v>18.5</v>
       </c>
       <c r="D176">
-        <v>20.09394264221191</v>
+        <v>18.21604347229004</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -3893,7 +3893,7 @@
         <v>16.20000076293945</v>
       </c>
       <c r="D177">
-        <v>12.94467830657959</v>
+        <v>10.61363124847412</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -3907,7 +3907,7 @@
         <v>0</v>
       </c>
       <c r="D178">
-        <v>2.322342157363892</v>
+        <v>2.99941349029541</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -3921,7 +3921,7 @@
         <v>25.29999923706055</v>
       </c>
       <c r="D179">
-        <v>18.27728462219238</v>
+        <v>20.64385032653809</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -3935,7 +3935,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D180">
-        <v>10.77716159820557</v>
+        <v>9.42723274230957</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -3949,7 +3949,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D181">
-        <v>6.18427848815918</v>
+        <v>6.618971347808838</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -3963,7 +3963,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D182">
-        <v>6.917810440063477</v>
+        <v>7.336628913879395</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -3977,7 +3977,7 @@
         <v>24</v>
       </c>
       <c r="D183">
-        <v>12.28733825683594</v>
+        <v>12.14627647399902</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -3991,7 +3991,7 @@
         <v>9</v>
       </c>
       <c r="D184">
-        <v>5.078603744506836</v>
+        <v>2.352642059326172</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4005,7 +4005,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D185">
-        <v>5.168028831481934</v>
+        <v>4.456490993499756</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4019,7 +4019,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D186">
-        <v>4.084980964660645</v>
+        <v>4.938425064086914</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4033,7 +4033,7 @@
         <v>5</v>
       </c>
       <c r="D187">
-        <v>4.352102279663086</v>
+        <v>3.989704608917236</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4047,7 +4047,7 @@
         <v>10.69999980926514</v>
       </c>
       <c r="D188">
-        <v>9.343849182128906</v>
+        <v>9.404133796691895</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4061,7 +4061,7 @@
         <v>23.79999923706055</v>
       </c>
       <c r="D189">
-        <v>16.15518569946289</v>
+        <v>16.1612434387207</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4075,7 +4075,7 @@
         <v>2</v>
       </c>
       <c r="D190">
-        <v>2.761302709579468</v>
+        <v>3.062991142272949</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4089,7 +4089,7 @@
         <v>0.5</v>
       </c>
       <c r="D191">
-        <v>3.43683385848999</v>
+        <v>3.772968769073486</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4103,7 +4103,7 @@
         <v>38.79999923706055</v>
       </c>
       <c r="D192">
-        <v>22.94489288330078</v>
+        <v>25.54085922241211</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4117,7 +4117,7 @@
         <v>17.70000076293945</v>
       </c>
       <c r="D193">
-        <v>18.0965747833252</v>
+        <v>17.12102317810059</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4131,7 +4131,7 @@
         <v>13.30000019073486</v>
       </c>
       <c r="D194">
-        <v>6.600588798522949</v>
+        <v>6.777970790863037</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4145,7 +4145,7 @@
         <v>18.39999961853027</v>
       </c>
       <c r="D195">
-        <v>18.74062728881836</v>
+        <v>18.47437286376953</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4159,7 +4159,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="D196">
-        <v>6.125857353210449</v>
+        <v>4.91732120513916</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4173,7 +4173,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D197">
-        <v>3.577345132827759</v>
+        <v>3.855204582214355</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4187,7 +4187,7 @@
         <v>2</v>
       </c>
       <c r="D198">
-        <v>1.840115785598755</v>
+        <v>2.435634613037109</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4201,7 +4201,7 @@
         <v>13.5</v>
       </c>
       <c r="D199">
-        <v>6.89094352722168</v>
+        <v>8.405445098876953</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4215,7 +4215,7 @@
         <v>16.39999961853027</v>
       </c>
       <c r="D200">
-        <v>9.805027008056641</v>
+        <v>9.530055999755859</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4229,7 +4229,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D201">
-        <v>7.689697265625</v>
+        <v>10.35928821563721</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4243,7 +4243,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D202">
-        <v>3.00916051864624</v>
+        <v>3.071174144744873</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4257,7 +4257,7 @@
         <v>4</v>
       </c>
       <c r="D203">
-        <v>1.71578311920166</v>
+        <v>2.059102296829224</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4271,7 +4271,7 @@
         <v>14.5</v>
       </c>
       <c r="D204">
-        <v>7.217263221740723</v>
+        <v>9.150945663452148</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4285,7 +4285,7 @@
         <v>3.5</v>
       </c>
       <c r="D205">
-        <v>3.057750701904297</v>
+        <v>1.537377834320068</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4299,7 +4299,7 @@
         <v>4.5</v>
       </c>
       <c r="D206">
-        <v>3.961902618408203</v>
+        <v>3.345757484436035</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4313,7 +4313,7 @@
         <v>5</v>
       </c>
       <c r="D207">
-        <v>8.638806343078613</v>
+        <v>8.985422134399414</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4327,7 +4327,7 @@
         <v>16.29999923706055</v>
       </c>
       <c r="D208">
-        <v>12.90808296203613</v>
+        <v>11.9791145324707</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4341,7 +4341,7 @@
         <v>19.79999923706055</v>
       </c>
       <c r="D209">
-        <v>18.71563529968262</v>
+        <v>17.98358917236328</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4355,7 +4355,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D210">
-        <v>3.817866563796997</v>
+        <v>3.559708595275879</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4369,7 +4369,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D211">
-        <v>3.308340072631836</v>
+        <v>3.716173648834229</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4383,7 +4383,7 @@
         <v>23.39999961853027</v>
       </c>
       <c r="D212">
-        <v>20.2890739440918</v>
+        <v>20.46496963500977</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4397,7 +4397,7 @@
         <v>4.5</v>
       </c>
       <c r="D213">
-        <v>2.392518997192383</v>
+        <v>2.839995861053467</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4411,7 +4411,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D214">
-        <v>1.327821016311646</v>
+        <v>1.110049724578857</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4425,7 +4425,7 @@
         <v>8.699999809265137</v>
       </c>
       <c r="D215">
-        <v>6.757768630981445</v>
+        <v>7.20407247543335</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4439,7 +4439,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D216">
-        <v>5.962794303894043</v>
+        <v>6.765675067901611</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4453,7 +4453,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D217">
-        <v>1.85046660900116</v>
+        <v>1.888305425643921</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4467,7 +4467,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D218">
-        <v>3.674829006195068</v>
+        <v>3.892259120941162</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4481,7 +4481,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D219">
-        <v>6.363189697265625</v>
+        <v>2.937739372253418</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4495,7 +4495,7 @@
         <v>9</v>
       </c>
       <c r="D220">
-        <v>7.996867179870605</v>
+        <v>8.824023246765137</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4509,7 +4509,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D221">
-        <v>3.503204107284546</v>
+        <v>3.294179439544678</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4523,7 +4523,7 @@
         <v>34.70000076293945</v>
       </c>
       <c r="D222">
-        <v>16.87948036193848</v>
+        <v>10.26025485992432</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4537,7 +4537,7 @@
         <v>11.19999980926514</v>
       </c>
       <c r="D223">
-        <v>1.874282121658325</v>
+        <v>2.316936016082764</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4551,7 +4551,7 @@
         <v>17.10000038146973</v>
       </c>
       <c r="D224">
-        <v>13.09951210021973</v>
+        <v>10.74558258056641</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4565,7 +4565,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D225">
-        <v>3.217941045761108</v>
+        <v>2.308130741119385</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4579,7 +4579,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D226">
-        <v>2.07046365737915</v>
+        <v>1.819805145263672</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4593,7 +4593,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D227">
-        <v>5.583184242248535</v>
+        <v>4.670764923095703</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4607,7 +4607,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D228">
-        <v>2.275840044021606</v>
+        <v>2.910910844802856</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4621,7 +4621,7 @@
         <v>8</v>
       </c>
       <c r="D229">
-        <v>2.362075090408325</v>
+        <v>2.656970977783203</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4635,7 +4635,7 @@
         <v>1.5</v>
       </c>
       <c r="D230">
-        <v>1.525957107543945</v>
+        <v>1.687735319137573</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4649,7 +4649,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D231">
-        <v>2.454981803894043</v>
+        <v>2.989400863647461</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4663,7 +4663,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D232">
-        <v>1.374470710754395</v>
+        <v>1.102658271789551</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4677,7 +4677,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D233">
-        <v>8.767765045166016</v>
+        <v>4.74846887588501</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4691,7 +4691,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D234">
-        <v>4.19808292388916</v>
+        <v>3.764496803283691</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4705,7 +4705,7 @@
         <v>22.20000076293945</v>
       </c>
       <c r="D235">
-        <v>16.68508720397949</v>
+        <v>18.43524551391602</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4719,7 +4719,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D236">
-        <v>8.590862274169922</v>
+        <v>8.083800315856934</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4733,7 +4733,7 @@
         <v>14.39999961853027</v>
       </c>
       <c r="D237">
-        <v>7.978782653808594</v>
+        <v>8.568339347839355</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4747,7 +4747,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D238">
-        <v>3.607202291488647</v>
+        <v>3.842721462249756</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4761,7 +4761,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D239">
-        <v>3.555639505386353</v>
+        <v>2.37946081161499</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4775,7 +4775,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D240">
-        <v>1.432796955108643</v>
+        <v>1.218530893325806</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4789,7 +4789,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D241">
-        <v>2.249720096588135</v>
+        <v>3.182793617248535</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4803,7 +4803,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="D242">
-        <v>7.116223335266113</v>
+        <v>7.359102249145508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4817,7 +4817,7 @@
         <v>11.19999980926514</v>
       </c>
       <c r="D243">
-        <v>4.699331283569336</v>
+        <v>4.374417781829834</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4831,7 +4831,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D244">
-        <v>1.611441016197205</v>
+        <v>1.439473986625671</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4845,7 +4845,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D245">
-        <v>3.968199014663696</v>
+        <v>5.780862331390381</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -4859,7 +4859,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D246">
-        <v>6.732600212097168</v>
+        <v>6.823513507843018</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -4873,7 +4873,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D247">
-        <v>1.422865867614746</v>
+        <v>1.310710430145264</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -4887,7 +4887,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D248">
-        <v>5.338153839111328</v>
+        <v>6.678741931915283</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -4901,7 +4901,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D249">
-        <v>3.685857057571411</v>
+        <v>2.527823925018311</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -4915,7 +4915,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D250">
-        <v>3.231518983840942</v>
+        <v>2.682746887207031</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -4929,7 +4929,7 @@
         <v>7.5</v>
       </c>
       <c r="D251">
-        <v>6.957600593566895</v>
+        <v>6.941362857818604</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -4943,7 +4943,7 @@
         <v>20.89999961853027</v>
       </c>
       <c r="D252">
-        <v>13.47820281982422</v>
+        <v>13.66719627380371</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -4957,7 +4957,7 @@
         <v>15.60000038146973</v>
       </c>
       <c r="D253">
-        <v>18.39334678649902</v>
+        <v>16.36503410339355</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -4971,7 +4971,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D254">
-        <v>5.878046989440918</v>
+        <v>3.950889110565186</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -4985,7 +4985,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D255">
-        <v>1.992311596870422</v>
+        <v>2.140681266784668</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -4999,7 +4999,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D256">
-        <v>2.248898983001709</v>
+        <v>4.179018974304199</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -5013,7 +5013,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D257">
-        <v>5.415265083312988</v>
+        <v>6.356335639953613</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -5027,7 +5027,7 @@
         <v>12.39999961853027</v>
       </c>
       <c r="D258">
-        <v>8.326384544372559</v>
+        <v>9.014833450317383</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -5041,7 +5041,7 @@
         <v>9.800000190734863</v>
       </c>
       <c r="D259">
-        <v>8.114079475402832</v>
+        <v>7.904224395751953</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -5055,7 +5055,7 @@
         <v>10.5</v>
       </c>
       <c r="D260">
-        <v>4.19666576385498</v>
+        <v>7.961155414581299</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -5069,7 +5069,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D261">
-        <v>4.256475925445557</v>
+        <v>4.197977542877197</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -5083,7 +5083,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D262">
-        <v>4.555230617523193</v>
+        <v>4.450699806213379</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -5097,7 +5097,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D263">
-        <v>1.597227334976196</v>
+        <v>1.658625841140747</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -5111,7 +5111,7 @@
         <v>5</v>
       </c>
       <c r="D264">
-        <v>1.50791072845459</v>
+        <v>2.289651393890381</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -5125,7 +5125,7 @@
         <v>15.5</v>
       </c>
       <c r="D265">
-        <v>10.77658653259277</v>
+        <v>8.225862503051758</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -5139,7 +5139,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D266">
-        <v>1.643797397613525</v>
+        <v>1.308295726776123</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -5153,7 +5153,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D267">
-        <v>3.774715662002563</v>
+        <v>3.349018573760986</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -5167,7 +5167,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D268">
-        <v>3.501002550125122</v>
+        <v>3.217193126678467</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -5181,7 +5181,7 @@
         <v>18.89999961853027</v>
       </c>
       <c r="D269">
-        <v>9.655857086181641</v>
+        <v>9.817832946777344</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -5195,7 +5195,7 @@
         <v>8.600000381469727</v>
       </c>
       <c r="D270">
-        <v>4.759890556335449</v>
+        <v>4.705924034118652</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -5209,7 +5209,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D271">
-        <v>2.300195932388306</v>
+        <v>2.972474575042725</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -5223,7 +5223,7 @@
         <v>18.20000076293945</v>
       </c>
       <c r="D272">
-        <v>21.04650497436523</v>
+        <v>19.78055000305176</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -5237,7 +5237,7 @@
         <v>20.79999923706055</v>
       </c>
       <c r="D273">
-        <v>11.71134757995605</v>
+        <v>15.41412544250488</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -5251,7 +5251,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D274">
-        <v>3.232113599777222</v>
+        <v>4.073031425476074</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -5265,7 +5265,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D275">
-        <v>3.854705333709717</v>
+        <v>3.242852210998535</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -5279,7 +5279,7 @@
         <v>9.300000190734863</v>
       </c>
       <c r="D276">
-        <v>3.332095146179199</v>
+        <v>5.230639457702637</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -5293,7 +5293,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D277">
-        <v>3.593841791152954</v>
+        <v>2.977826595306396</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -5307,7 +5307,7 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>9.867447853088379</v>
+        <v>10.07291221618652</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -5321,7 +5321,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D279">
-        <v>5.164867401123047</v>
+        <v>7.929970264434814</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -5335,7 +5335,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D280">
-        <v>3.653222322463989</v>
+        <v>2.384139060974121</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -5349,7 +5349,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D281">
-        <v>6.705563545227051</v>
+        <v>5.161214351654053</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -5363,7 +5363,7 @@
         <v>15.69999980926514</v>
       </c>
       <c r="D282">
-        <v>6.927373886108398</v>
+        <v>6.998618602752686</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -5377,7 +5377,7 @@
         <v>3</v>
       </c>
       <c r="D283">
-        <v>2.394837856292725</v>
+        <v>3.216172695159912</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -5391,7 +5391,7 @@
         <v>0</v>
       </c>
       <c r="D284">
-        <v>1.351555824279785</v>
+        <v>1.116015434265137</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -5405,7 +5405,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D285">
-        <v>4.010664939880371</v>
+        <v>4.032022476196289</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -5419,7 +5419,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D286">
-        <v>9.091353416442871</v>
+        <v>9.23906135559082</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -5433,7 +5433,7 @@
         <v>2</v>
       </c>
       <c r="D287">
-        <v>1.652742385864258</v>
+        <v>1.425940752029419</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -5447,7 +5447,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D288">
-        <v>3.234593629837036</v>
+        <v>2.352334976196289</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5461,7 +5461,7 @@
         <v>8</v>
       </c>
       <c r="D289">
-        <v>3.870932817459106</v>
+        <v>5.826769828796387</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5475,7 +5475,7 @@
         <v>11.30000019073486</v>
       </c>
       <c r="D290">
-        <v>8.876358032226562</v>
+        <v>9.549060821533203</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5489,7 +5489,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D291">
-        <v>4.191853523254395</v>
+        <v>4.23800802230835</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5503,7 +5503,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="D292">
-        <v>6.814811706542969</v>
+        <v>5.998371601104736</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5517,7 +5517,7 @@
         <v>7.5</v>
       </c>
       <c r="D293">
-        <v>3.833848714828491</v>
+        <v>5.329187870025635</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5531,7 +5531,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D294">
-        <v>14.89273071289062</v>
+        <v>13.11863708496094</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5545,7 +5545,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D295">
-        <v>1.842583179473877</v>
+        <v>2.899530410766602</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5559,7 +5559,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D296">
-        <v>2.341824531555176</v>
+        <v>2.079763889312744</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5573,7 +5573,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D297">
-        <v>4.684925079345703</v>
+        <v>5.20965576171875</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5587,7 +5587,7 @@
         <v>15.60000038146973</v>
       </c>
       <c r="D298">
-        <v>13.81537437438965</v>
+        <v>12.52949905395508</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5601,7 +5601,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D299">
-        <v>4.89387321472168</v>
+        <v>5.271233558654785</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5615,7 +5615,7 @@
         <v>11.5</v>
       </c>
       <c r="D300">
-        <v>6.218173027038574</v>
+        <v>7.954739093780518</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5629,7 +5629,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D301">
-        <v>2.324534177780151</v>
+        <v>3.015669822692871</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5643,7 +5643,7 @@
         <v>12.60000038146973</v>
       </c>
       <c r="D302">
-        <v>3.993615627288818</v>
+        <v>5.741651058197021</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5657,7 +5657,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D303">
-        <v>1.387904047966003</v>
+        <v>1.089827060699463</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5671,7 +5671,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D304">
-        <v>1.346169710159302</v>
+        <v>1.124424457550049</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -5685,7 +5685,7 @@
         <v>11.69999980926514</v>
       </c>
       <c r="D305">
-        <v>8.926091194152832</v>
+        <v>9.217599868774414</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -5699,7 +5699,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D306">
-        <v>2.600854396820068</v>
+        <v>2.625902652740479</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5713,7 +5713,7 @@
         <v>5.5</v>
       </c>
       <c r="D307">
-        <v>2.420612812042236</v>
+        <v>2.997586727142334</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5727,7 +5727,7 @@
         <v>5.5</v>
       </c>
       <c r="D308">
-        <v>3.568471431732178</v>
+        <v>3.086865425109863</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -5741,7 +5741,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D309">
-        <v>3.661354780197144</v>
+        <v>3.250623226165771</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -5755,7 +5755,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D310">
-        <v>4.588163375854492</v>
+        <v>4.593647003173828</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -5769,7 +5769,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D311">
-        <v>5.936688423156738</v>
+        <v>6.771158695220947</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -5783,7 +5783,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D312">
-        <v>2.459025382995605</v>
+        <v>2.626487731933594</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -5797,7 +5797,7 @@
         <v>11.5</v>
       </c>
       <c r="D313">
-        <v>7.355585098266602</v>
+        <v>7.649861335754395</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -5811,7 +5811,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D314">
-        <v>3.726278305053711</v>
+        <v>3.335094928741455</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -5825,7 +5825,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D315">
-        <v>3.422104835510254</v>
+        <v>3.326002597808838</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -5839,7 +5839,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D316">
-        <v>5.176148414611816</v>
+        <v>5.155313968658447</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -5853,7 +5853,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D317">
-        <v>3.651198387145996</v>
+        <v>3.140475273132324</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -5867,7 +5867,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D318">
-        <v>6.932984352111816</v>
+        <v>6.6775221824646</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -5881,7 +5881,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D319">
-        <v>1.336445927619934</v>
+        <v>1.148628950119019</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -5895,7 +5895,7 @@
         <v>13.30000019073486</v>
       </c>
       <c r="D320">
-        <v>9.82008171081543</v>
+        <v>10.00678062438965</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -5909,7 +5909,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D321">
-        <v>3.886979341506958</v>
+        <v>3.118091583251953</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -5923,7 +5923,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D322">
-        <v>6.267874717712402</v>
+        <v>7.225418090820312</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -5937,7 +5937,7 @@
         <v>20.39999961853027</v>
       </c>
       <c r="D323">
-        <v>18.79689598083496</v>
+        <v>17.2208309173584</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -5951,7 +5951,7 @@
         <v>12.69999980926514</v>
       </c>
       <c r="D324">
-        <v>8.739326477050781</v>
+        <v>10.24961185455322</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -5965,7 +5965,7 @@
         <v>22.39999961853027</v>
       </c>
       <c r="D325">
-        <v>19.31253433227539</v>
+        <v>18.7121639251709</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -5979,7 +5979,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D326">
-        <v>4.621774196624756</v>
+        <v>4.31983757019043</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -5993,7 +5993,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D327">
-        <v>5.043560981750488</v>
+        <v>6.368184089660645</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -6007,7 +6007,7 @@
         <v>17.29999923706055</v>
       </c>
       <c r="D328">
-        <v>6.748332977294922</v>
+        <v>7.514163494110107</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -6021,7 +6021,7 @@
         <v>21.5</v>
       </c>
       <c r="D329">
-        <v>12.24875259399414</v>
+        <v>9.626968383789062</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -6035,7 +6035,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D330">
-        <v>1.348132252693176</v>
+        <v>1.114761114120483</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -6049,7 +6049,7 @@
         <v>1</v>
       </c>
       <c r="D331">
-        <v>5.008923530578613</v>
+        <v>5.543757915496826</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -6063,7 +6063,7 @@
         <v>16.60000038146973</v>
       </c>
       <c r="D332">
-        <v>15.9185905456543</v>
+        <v>16.60029411315918</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -6077,7 +6077,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D333">
-        <v>6.76319408416748</v>
+        <v>3.811404705047607</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -6091,7 +6091,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D334">
-        <v>1.456552267074585</v>
+        <v>1.753141641616821</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -6105,7 +6105,7 @@
         <v>14.39999961853027</v>
       </c>
       <c r="D335">
-        <v>8.383034706115723</v>
+        <v>8.931661605834961</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -6119,7 +6119,7 @@
         <v>12.5</v>
       </c>
       <c r="D336">
-        <v>8.383932113647461</v>
+        <v>8.74083423614502</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -6133,7 +6133,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D337">
-        <v>5.565197944641113</v>
+        <v>6.721883296966553</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -6147,7 +6147,7 @@
         <v>10.60000038146973</v>
       </c>
       <c r="D338">
-        <v>6.710107803344727</v>
+        <v>7.05681037902832</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -6161,7 +6161,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D339">
-        <v>1.489796161651611</v>
+        <v>1.317912101745605</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -6175,7 +6175,7 @@
         <v>1</v>
       </c>
       <c r="D340">
-        <v>2.340133190155029</v>
+        <v>2.764529228210449</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -6189,7 +6189,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D341">
-        <v>1.370728373527527</v>
+        <v>1.129240751266479</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -6203,7 +6203,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D342">
-        <v>1.4859459400177</v>
+        <v>1.304009675979614</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -6217,7 +6217,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D343">
-        <v>3.750528573989868</v>
+        <v>4.30812931060791</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -6231,7 +6231,7 @@
         <v>14.10000038146973</v>
       </c>
       <c r="D344">
-        <v>8.316226959228516</v>
+        <v>7.889402866363525</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -6245,7 +6245,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D345">
-        <v>6.073741912841797</v>
+        <v>10.37486457824707</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -6259,7 +6259,7 @@
         <v>7</v>
       </c>
       <c r="D346">
-        <v>4.21251392364502</v>
+        <v>4.155261993408203</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -6273,7 +6273,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="D347">
-        <v>9.136421203613281</v>
+        <v>10.79771137237549</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -6287,7 +6287,7 @@
         <v>13.10000038146973</v>
       </c>
       <c r="D348">
-        <v>12.22770118713379</v>
+        <v>13.17896747589111</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -6301,7 +6301,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D349">
-        <v>3.621054649353027</v>
+        <v>2.645671844482422</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -6315,7 +6315,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D350">
-        <v>2.546380758285522</v>
+        <v>2.627066135406494</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6329,7 +6329,7 @@
         <v>4</v>
       </c>
       <c r="D351">
-        <v>3.128710746765137</v>
+        <v>3.749976634979248</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -6343,7 +6343,7 @@
         <v>0</v>
       </c>
       <c r="D352">
-        <v>14.85823440551758</v>
+        <v>14.03624248504639</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -6357,7 +6357,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D353">
-        <v>2.940729379653931</v>
+        <v>1.367629528045654</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -6371,7 +6371,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D354">
-        <v>5.221193313598633</v>
+        <v>5.066810607910156</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -6385,7 +6385,7 @@
         <v>14.19999980926514</v>
       </c>
       <c r="D355">
-        <v>6.587459564208984</v>
+        <v>7.75495433807373</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -6399,7 +6399,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D356">
-        <v>3.458405494689941</v>
+        <v>8.033298492431641</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -6413,7 +6413,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D357">
-        <v>3.551658153533936</v>
+        <v>3.23193883895874</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -6427,7 +6427,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D358">
-        <v>4.585684776306152</v>
+        <v>2.558931350708008</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -6441,7 +6441,7 @@
         <v>11.30000019073486</v>
       </c>
       <c r="D359">
-        <v>8.32408618927002</v>
+        <v>8.731882095336914</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -6455,7 +6455,7 @@
         <v>0.5</v>
       </c>
       <c r="D360">
-        <v>1.388513565063477</v>
+        <v>1.414273619651794</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -6469,7 +6469,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D361">
-        <v>6.360899925231934</v>
+        <v>7.101290225982666</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -6483,7 +6483,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D362">
-        <v>3.986928224563599</v>
+        <v>3.578917503356934</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6497,7 +6497,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D363">
-        <v>3.664124250411987</v>
+        <v>2.422982692718506</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -6511,7 +6511,7 @@
         <v>6.5</v>
       </c>
       <c r="D364">
-        <v>2.9908127784729</v>
+        <v>3.302308082580566</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -6525,7 +6525,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D365">
-        <v>1.924726963043213</v>
+        <v>2.187134265899658</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -6539,7 +6539,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D366">
-        <v>3.543005228042603</v>
+        <v>3.893470287322998</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -6553,7 +6553,7 @@
         <v>11.39999961853027</v>
       </c>
       <c r="D367">
-        <v>8.848923683166504</v>
+        <v>10.05227184295654</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -6567,7 +6567,7 @@
         <v>40.90000152587891</v>
       </c>
       <c r="D368">
-        <v>30.61225891113281</v>
+        <v>33.75124359130859</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -6581,7 +6581,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D369">
-        <v>2.853336095809937</v>
+        <v>2.646862506866455</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -6595,7 +6595,7 @@
         <v>17.5</v>
       </c>
       <c r="D370">
-        <v>15.75072288513184</v>
+        <v>15.27095794677734</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -6609,7 +6609,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D371">
-        <v>2.941614151000977</v>
+        <v>3.048141479492188</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -6623,7 +6623,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D372">
-        <v>4.013022422790527</v>
+        <v>4.151137351989746</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -6637,7 +6637,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D373">
-        <v>4.166449546813965</v>
+        <v>3.995034694671631</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -6651,7 +6651,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D374">
-        <v>5.284881591796875</v>
+        <v>6.204345226287842</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -6665,7 +6665,7 @@
         <v>20.39999961853027</v>
       </c>
       <c r="D375">
-        <v>6.561841011047363</v>
+        <v>6.858314990997314</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -6679,7 +6679,7 @@
         <v>0.5</v>
       </c>
       <c r="D376">
-        <v>5.633686065673828</v>
+        <v>6.141602993011475</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -6693,7 +6693,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D377">
-        <v>3.656391143798828</v>
+        <v>4.135557174682617</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -6707,7 +6707,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D378">
-        <v>6.006755828857422</v>
+        <v>8.460089683532715</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -6721,7 +6721,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D379">
-        <v>3.772130966186523</v>
+        <v>3.368951320648193</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -6735,7 +6735,7 @@
         <v>7</v>
       </c>
       <c r="D380">
-        <v>7.947498321533203</v>
+        <v>9.301877975463867</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -6749,7 +6749,7 @@
         <v>14.19999980926514</v>
       </c>
       <c r="D381">
-        <v>6.651037216186523</v>
+        <v>7.185328960418701</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -6763,7 +6763,7 @@
         <v>1.5</v>
       </c>
       <c r="D382">
-        <v>1.339522480964661</v>
+        <v>1.115048170089722</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -6777,7 +6777,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D383">
-        <v>1.4351806640625</v>
+        <v>1.299751400947571</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -6791,7 +6791,7 @@
         <v>2</v>
       </c>
       <c r="D384">
-        <v>2.34482479095459</v>
+        <v>2.675691604614258</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -6805,7 +6805,7 @@
         <v>8</v>
       </c>
       <c r="D385">
-        <v>5.835264205932617</v>
+        <v>7.239320278167725</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -6819,7 +6819,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D386">
-        <v>4.439184665679932</v>
+        <v>4.208087921142578</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -6833,7 +6833,7 @@
         <v>11.5</v>
       </c>
       <c r="D387">
-        <v>9.185731887817383</v>
+        <v>9.312333106994629</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -6847,7 +6847,7 @@
         <v>8.5</v>
       </c>
       <c r="D388">
-        <v>9.321571350097656</v>
+        <v>9.366036415100098</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -6861,7 +6861,7 @@
         <v>2.5</v>
       </c>
       <c r="D389">
-        <v>2.939432621002197</v>
+        <v>3.50248908996582</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -6875,7 +6875,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D390">
-        <v>3.796563625335693</v>
+        <v>2.777878761291504</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -6889,7 +6889,7 @@
         <v>9.800000190734863</v>
       </c>
       <c r="D391">
-        <v>7.991997718811035</v>
+        <v>9.181371688842773</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -6903,7 +6903,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D392">
-        <v>3.215259790420532</v>
+        <v>2.734375</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -6917,7 +6917,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D393">
-        <v>1.31891393661499</v>
+        <v>1.167240977287292</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -6931,7 +6931,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D394">
-        <v>5.36524772644043</v>
+        <v>2.518518447875977</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -6945,7 +6945,7 @@
         <v>38</v>
       </c>
       <c r="D395">
-        <v>20.14743423461914</v>
+        <v>23.6938304901123</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -6959,7 +6959,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D396">
-        <v>3.024527072906494</v>
+        <v>1.506182789802551</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -6973,7 +6973,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D397">
-        <v>8.748648643493652</v>
+        <v>10.4548511505127</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -6987,7 +6987,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D398">
-        <v>6.992732048034668</v>
+        <v>7.430026531219482</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -7001,7 +7001,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D399">
-        <v>7.450523376464844</v>
+        <v>4.824193000793457</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -7015,7 +7015,7 @@
         <v>10.10000038146973</v>
       </c>
       <c r="D400">
-        <v>2.579944133758545</v>
+        <v>3.362197875976562</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -7029,7 +7029,7 @@
         <v>0</v>
       </c>
       <c r="D401">
-        <v>2.260697841644287</v>
+        <v>1.361566543579102</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -7043,7 +7043,7 @@
         <v>9.5</v>
       </c>
       <c r="D402">
-        <v>3.566657304763794</v>
+        <v>2.735610485076904</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -7057,7 +7057,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D403">
-        <v>3.826821565628052</v>
+        <v>4.049623966217041</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -7071,7 +7071,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D404">
-        <v>3.580607175827026</v>
+        <v>3.699066638946533</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -7085,7 +7085,7 @@
         <v>19.39999961853027</v>
       </c>
       <c r="D405">
-        <v>17.17262268066406</v>
+        <v>17.86977958679199</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -7099,7 +7099,7 @@
         <v>11.5</v>
       </c>
       <c r="D406">
-        <v>8.83228874206543</v>
+        <v>9.10956859588623</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -7113,7 +7113,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D407">
-        <v>1.904188990592957</v>
+        <v>1.924096584320068</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -7127,7 +7127,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D408">
-        <v>2.728944540023804</v>
+        <v>2.654827356338501</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -7141,7 +7141,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D409">
-        <v>4.182973861694336</v>
+        <v>4.420565128326416</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -7155,7 +7155,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D410">
-        <v>8.462640762329102</v>
+        <v>8.757803916931152</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -7169,7 +7169,7 @@
         <v>10.80000019073486</v>
       </c>
       <c r="D411">
-        <v>4.170346260070801</v>
+        <v>4.233895301818848</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -7183,7 +7183,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D412">
-        <v>4.072071075439453</v>
+        <v>3.05423641204834</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -7197,7 +7197,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D413">
-        <v>3.444746255874634</v>
+        <v>2.420095443725586</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -7211,7 +7211,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D414">
-        <v>3.377840757369995</v>
+        <v>3.734099388122559</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -7225,7 +7225,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D415">
-        <v>2.372322797775269</v>
+        <v>2.889583587646484</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -7239,7 +7239,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D416">
-        <v>3.859635591506958</v>
+        <v>4.091434955596924</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -7253,7 +7253,7 @@
         <v>14.39999961853027</v>
       </c>
       <c r="D417">
-        <v>5.140022277832031</v>
+        <v>7.212249755859375</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -7267,7 +7267,7 @@
         <v>20.70000076293945</v>
       </c>
       <c r="D418">
-        <v>18.41895294189453</v>
+        <v>18.18470573425293</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -7281,7 +7281,7 @@
         <v>12.30000019073486</v>
       </c>
       <c r="D419">
-        <v>3.340367555618286</v>
+        <v>7.073269367218018</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -7295,7 +7295,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D420">
-        <v>2.542572021484375</v>
+        <v>2.596180438995361</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -7309,7 +7309,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D421">
-        <v>3.043107271194458</v>
+        <v>1.915610671043396</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -7323,7 +7323,7 @@
         <v>14.39999961853027</v>
       </c>
       <c r="D422">
-        <v>9.087617874145508</v>
+        <v>9.18696403503418</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -7337,7 +7337,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D423">
-        <v>2.592155456542969</v>
+        <v>2.900104999542236</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -7351,7 +7351,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D424">
-        <v>1.346325397491455</v>
+        <v>1.131099462509155</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -7365,7 +7365,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D425">
-        <v>1.337025880813599</v>
+        <v>1.112825870513916</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -7379,7 +7379,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D426">
-        <v>1.292244076728821</v>
+        <v>1.202947378158569</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -7393,7 +7393,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D427">
-        <v>1.63454270362854</v>
+        <v>2.639974594116211</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -7407,7 +7407,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D428">
-        <v>5.18360424041748</v>
+        <v>4.830267429351807</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -7421,7 +7421,7 @@
         <v>3.5</v>
       </c>
       <c r="D429">
-        <v>6.574422836303711</v>
+        <v>8.609015464782715</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -7435,7 +7435,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D430">
-        <v>1.49235737323761</v>
+        <v>1.3801509141922</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -7449,7 +7449,7 @@
         <v>29.60000038146973</v>
       </c>
       <c r="D431">
-        <v>23.99050521850586</v>
+        <v>23.51749038696289</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -7463,7 +7463,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D432">
-        <v>3.606911420822144</v>
+        <v>2.094480037689209</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -7477,7 +7477,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D433">
-        <v>2.732123374938965</v>
+        <v>3.451737880706787</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -7491,7 +7491,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D434">
-        <v>2.424395799636841</v>
+        <v>2.623798370361328</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -7505,7 +7505,7 @@
         <v>19.5</v>
       </c>
       <c r="D435">
-        <v>20.84263610839844</v>
+        <v>18.70026206970215</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -7519,7 +7519,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D436">
-        <v>4.524104118347168</v>
+        <v>4.411855220794678</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -7533,7 +7533,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D437">
-        <v>3.702968597412109</v>
+        <v>4.023996353149414</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -7547,7 +7547,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D438">
-        <v>3.805634260177612</v>
+        <v>3.676795959472656</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -7561,7 +7561,7 @@
         <v>18.5</v>
       </c>
       <c r="D439">
-        <v>5.603775024414062</v>
+        <v>5.64661169052124</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -7575,7 +7575,7 @@
         <v>18</v>
       </c>
       <c r="D440">
-        <v>15.22418117523193</v>
+        <v>14.10954856872559</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -7589,7 +7589,7 @@
         <v>8.5</v>
       </c>
       <c r="D441">
-        <v>6.975569725036621</v>
+        <v>6.563520908355713</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -7603,7 +7603,7 @@
         <v>9</v>
       </c>
       <c r="D442">
-        <v>8.490413665771484</v>
+        <v>8.096555709838867</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -7617,7 +7617,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D443">
-        <v>1.382015466690063</v>
+        <v>1.098132848739624</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -7631,7 +7631,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D444">
-        <v>1.521620988845825</v>
+        <v>1.372869491577148</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -7645,7 +7645,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D445">
-        <v>3.403239011764526</v>
+        <v>2.239407062530518</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -7659,7 +7659,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D446">
-        <v>1.355227708816528</v>
+        <v>1.132265567779541</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -7673,7 +7673,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D447">
-        <v>2.512621879577637</v>
+        <v>2.432875156402588</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -7687,7 +7687,7 @@
         <v>14.69999980926514</v>
       </c>
       <c r="D448">
-        <v>6.97357177734375</v>
+        <v>10.63112831115723</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -7701,7 +7701,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D449">
-        <v>6.981822967529297</v>
+        <v>8.251631736755371</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -7715,7 +7715,7 @@
         <v>16.60000038146973</v>
       </c>
       <c r="D450">
-        <v>16.16349983215332</v>
+        <v>13.52529525756836</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -7729,7 +7729,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D451">
-        <v>4.393544673919678</v>
+        <v>4.62470531463623</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -7743,7 +7743,7 @@
         <v>9</v>
       </c>
       <c r="D452">
-        <v>5.028444766998291</v>
+        <v>6.105467319488525</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -7757,7 +7757,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D453">
-        <v>2.394038677215576</v>
+        <v>3.561156749725342</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -7771,7 +7771,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D454">
-        <v>4.759716987609863</v>
+        <v>7.014976978302002</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -7785,7 +7785,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D455">
-        <v>4.33812427520752</v>
+        <v>4.654299259185791</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -7799,7 +7799,7 @@
         <v>39.90000152587891</v>
       </c>
       <c r="D456">
-        <v>24.82209968566895</v>
+        <v>25.28400993347168</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -7813,7 +7813,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D457">
-        <v>2.931849956512451</v>
+        <v>3.309779167175293</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -7827,7 +7827,7 @@
         <v>23.70000076293945</v>
       </c>
       <c r="D458">
-        <v>18.50786209106445</v>
+        <v>19.98217964172363</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -7841,7 +7841,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D459">
-        <v>1.334368824958801</v>
+        <v>1.233672857284546</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -7855,7 +7855,7 @@
         <v>10.5</v>
       </c>
       <c r="D460">
-        <v>3.875076770782471</v>
+        <v>3.695431709289551</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -7869,7 +7869,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D461">
-        <v>3.219760179519653</v>
+        <v>5.457176685333252</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -7883,7 +7883,7 @@
         <v>18.79999923706055</v>
       </c>
       <c r="D462">
-        <v>18.50066757202148</v>
+        <v>17.23107528686523</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -7897,7 +7897,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D463">
-        <v>8.460178375244141</v>
+        <v>4.430418968200684</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -7911,7 +7911,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D464">
-        <v>1.558417201042175</v>
+        <v>1.678932785987854</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -7925,7 +7925,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D465">
-        <v>1.351160645484924</v>
+        <v>1.116353273391724</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -7939,7 +7939,7 @@
         <v>2</v>
       </c>
       <c r="D466">
-        <v>3.8626549243927</v>
+        <v>3.648388862609863</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -7953,7 +7953,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D467">
-        <v>1.470855355262756</v>
+        <v>2.050849676132202</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -7967,7 +7967,7 @@
         <v>11.60000038146973</v>
       </c>
       <c r="D468">
-        <v>4.006906509399414</v>
+        <v>3.560720443725586</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -7981,7 +7981,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D469">
-        <v>3.013162851333618</v>
+        <v>3.641138553619385</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -7995,7 +7995,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D470">
-        <v>2.484813690185547</v>
+        <v>2.801373958587646</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -8009,7 +8009,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D471">
-        <v>7.085720062255859</v>
+        <v>8.090373992919922</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -8023,7 +8023,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D472">
-        <v>3.216091156005859</v>
+        <v>3.468591213226318</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -8037,7 +8037,7 @@
         <v>1.5</v>
       </c>
       <c r="D473">
-        <v>3.36253809928894</v>
+        <v>3.580474853515625</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -8051,7 +8051,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D474">
-        <v>1.357295036315918</v>
+        <v>1.115474104881287</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -8065,7 +8065,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D475">
-        <v>6.118821144104004</v>
+        <v>4.005447864532471</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -8079,7 +8079,7 @@
         <v>1</v>
       </c>
       <c r="D476">
-        <v>1.359707474708557</v>
+        <v>1.119132399559021</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -8093,7 +8093,7 @@
         <v>18.89999961853027</v>
       </c>
       <c r="D477">
-        <v>14.41605377197266</v>
+        <v>13.51226234436035</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -8107,7 +8107,7 @@
         <v>1.5</v>
       </c>
       <c r="D478">
-        <v>3.908133745193481</v>
+        <v>4.649077892303467</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -8121,7 +8121,7 @@
         <v>6.5</v>
       </c>
       <c r="D479">
-        <v>4.148813247680664</v>
+        <v>4.048567771911621</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -8135,7 +8135,7 @@
         <v>2</v>
       </c>
       <c r="D480">
-        <v>3.812198638916016</v>
+        <v>4.095733165740967</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -8149,7 +8149,7 @@
         <v>0.5</v>
       </c>
       <c r="D481">
-        <v>1.498044490814209</v>
+        <v>1.254554152488708</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -8163,7 +8163,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D482">
-        <v>3.795902967453003</v>
+        <v>2.334282398223877</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -8177,7 +8177,7 @@
         <v>24.79999923706055</v>
       </c>
       <c r="D483">
-        <v>15.6466588973999</v>
+        <v>16.77046585083008</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -8191,7 +8191,7 @@
         <v>5.5</v>
       </c>
       <c r="D484">
-        <v>2.424310207366943</v>
+        <v>3.401999473571777</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -8205,7 +8205,7 @@
         <v>9.100000381469727</v>
       </c>
       <c r="D485">
-        <v>3.391704559326172</v>
+        <v>2.561803817749023</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -8219,7 +8219,7 @@
         <v>5.5</v>
       </c>
       <c r="D486">
-        <v>2.646182537078857</v>
+        <v>3.504900932312012</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -8233,7 +8233,7 @@
         <v>15</v>
       </c>
       <c r="D487">
-        <v>10.96400833129883</v>
+        <v>9.87843132019043</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -8247,7 +8247,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D488">
-        <v>4.019685745239258</v>
+        <v>4.424246311187744</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -8261,7 +8261,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D489">
-        <v>2.316604852676392</v>
+        <v>2.800418615341187</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -8275,7 +8275,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D490">
-        <v>2.595096111297607</v>
+        <v>3.198325157165527</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -8289,7 +8289,7 @@
         <v>10.39999961853027</v>
       </c>
       <c r="D491">
-        <v>4.201452255249023</v>
+        <v>4.421566486358643</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -8303,7 +8303,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D492">
-        <v>6.965505599975586</v>
+        <v>6.973026752471924</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -8317,7 +8317,7 @@
         <v>12.19999980926514</v>
       </c>
       <c r="D493">
-        <v>6.445362091064453</v>
+        <v>7.033776760101318</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -8331,7 +8331,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D494">
-        <v>3.539839744567871</v>
+        <v>1.786539435386658</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -8345,7 +8345,7 @@
         <v>16.39999961853027</v>
       </c>
       <c r="D495">
-        <v>6.672693252563477</v>
+        <v>5.881213665008545</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -8359,7 +8359,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D496">
-        <v>3.803414344787598</v>
+        <v>3.574353218078613</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -8373,7 +8373,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D497">
-        <v>5.616394996643066</v>
+        <v>8.975131988525391</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -8387,7 +8387,7 @@
         <v>1.5</v>
       </c>
       <c r="D498">
-        <v>4.101917266845703</v>
+        <v>3.647427558898926</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -8401,7 +8401,7 @@
         <v>12.60000038146973</v>
       </c>
       <c r="D499">
-        <v>6.96015453338623</v>
+        <v>7.984537124633789</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -8415,7 +8415,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D500">
-        <v>3.629789113998413</v>
+        <v>3.345356464385986</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -8429,7 +8429,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D501">
-        <v>1.48422634601593</v>
+        <v>2.008510589599609</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -8443,7 +8443,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D502">
-        <v>5.377419471740723</v>
+        <v>5.299313068389893</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -8457,7 +8457,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D503">
-        <v>1.62859034538269</v>
+        <v>3.885490417480469</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -8471,7 +8471,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D504">
-        <v>2.45435619354248</v>
+        <v>2.84023380279541</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -8485,7 +8485,7 @@
         <v>13.60000038146973</v>
       </c>
       <c r="D505">
-        <v>7.636734962463379</v>
+        <v>9.856533050537109</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -8499,7 +8499,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D506">
-        <v>17.1937198638916</v>
+        <v>16.52106285095215</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -8513,7 +8513,7 @@
         <v>12.60000038146973</v>
       </c>
       <c r="D507">
-        <v>6.935788154602051</v>
+        <v>6.809800624847412</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -8527,7 +8527,7 @@
         <v>10.60000038146973</v>
       </c>
       <c r="D508">
-        <v>10.48505401611328</v>
+        <v>9.481260299682617</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -8541,7 +8541,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D509">
-        <v>4.117765426635742</v>
+        <v>4.318713188171387</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -8555,7 +8555,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D510">
-        <v>4.455177783966064</v>
+        <v>4.990777492523193</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -8569,7 +8569,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D511">
-        <v>1.492686986923218</v>
+        <v>2.589108943939209</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -8583,7 +8583,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D512">
-        <v>1.348677396774292</v>
+        <v>1.148186445236206</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -8597,7 +8597,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D513">
-        <v>1.379605293273926</v>
+        <v>1.579678177833557</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -8611,7 +8611,7 @@
         <v>1</v>
       </c>
       <c r="D514">
-        <v>3.800786972045898</v>
+        <v>4.170441150665283</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -8625,7 +8625,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D515">
-        <v>3.885146141052246</v>
+        <v>2.807748794555664</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -8639,7 +8639,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D516">
-        <v>1.331659197807312</v>
+        <v>1.180378317832947</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -8653,7 +8653,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D517">
-        <v>2.272662401199341</v>
+        <v>5.305288791656494</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -8667,7 +8667,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D518">
-        <v>3.997114419937134</v>
+        <v>4.031881332397461</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -8681,7 +8681,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D519">
-        <v>3.857291698455811</v>
+        <v>6.201406955718994</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -8695,7 +8695,7 @@
         <v>8</v>
       </c>
       <c r="D520">
-        <v>3.619886159896851</v>
+        <v>3.938211441040039</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -8709,7 +8709,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D521">
-        <v>4.262228965759277</v>
+        <v>4.661919593811035</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -8723,7 +8723,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D522">
-        <v>7.06365966796875</v>
+        <v>7.067913055419922</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -8737,7 +8737,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D523">
-        <v>6.406786918640137</v>
+        <v>6.28563404083252</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -8751,7 +8751,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D524">
-        <v>1.677228569984436</v>
+        <v>1.449696063995361</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -8765,7 +8765,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D525">
-        <v>5.148616790771484</v>
+        <v>5.09575891494751</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -8779,7 +8779,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D526">
-        <v>3.66846489906311</v>
+        <v>3.899747848510742</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -8793,7 +8793,7 @@
         <v>14</v>
       </c>
       <c r="D527">
-        <v>17.01399993896484</v>
+        <v>17.35146331787109</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -8807,7 +8807,7 @@
         <v>12.89999961853027</v>
       </c>
       <c r="D528">
-        <v>10.27228355407715</v>
+        <v>8.811176300048828</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -8821,7 +8821,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D529">
-        <v>3.772534847259521</v>
+        <v>3.643768787384033</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -8835,7 +8835,7 @@
         <v>3.5</v>
       </c>
       <c r="D530">
-        <v>3.564609527587891</v>
+        <v>3.005322456359863</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -8849,7 +8849,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D531">
-        <v>2.622520446777344</v>
+        <v>1.582513332366943</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -8863,7 +8863,7 @@
         <v>12.39999961853027</v>
       </c>
       <c r="D532">
-        <v>8.787067413330078</v>
+        <v>9.475667953491211</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -8877,7 +8877,7 @@
         <v>10.10000038146973</v>
       </c>
       <c r="D533">
-        <v>6.729946136474609</v>
+        <v>7.321089267730713</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -8891,7 +8891,7 @@
         <v>26</v>
       </c>
       <c r="D534">
-        <v>18.35348129272461</v>
+        <v>16.46302795410156</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -8905,7 +8905,7 @@
         <v>19.79999923706055</v>
       </c>
       <c r="D535">
-        <v>16.88312911987305</v>
+        <v>15.17555522918701</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -8919,7 +8919,7 @@
         <v>2</v>
       </c>
       <c r="D536">
-        <v>1.78603196144104</v>
+        <v>1.743593454360962</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -8933,7 +8933,7 @@
         <v>2.5</v>
       </c>
       <c r="D537">
-        <v>3.184603691101074</v>
+        <v>2.276192188262939</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -8947,7 +8947,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D538">
-        <v>2.473173856735229</v>
+        <v>3.243802547454834</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -8961,7 +8961,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D539">
-        <v>6.996026992797852</v>
+        <v>7.047445297241211</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -8975,7 +8975,7 @@
         <v>13</v>
       </c>
       <c r="D540">
-        <v>8.322802543640137</v>
+        <v>4.772282600402832</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -8989,7 +8989,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="D541">
-        <v>4.338247299194336</v>
+        <v>4.936538696289062</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -9003,7 +9003,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D542">
-        <v>3.654282331466675</v>
+        <v>4.835946083068848</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -9017,7 +9017,7 @@
         <v>15.19999980926514</v>
       </c>
       <c r="D543">
-        <v>13.77268028259277</v>
+        <v>12.29505920410156</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -9031,7 +9031,7 @@
         <v>7</v>
       </c>
       <c r="D544">
-        <v>17.27315711975098</v>
+        <v>16.90647888183594</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -9045,7 +9045,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D545">
-        <v>1.344959855079651</v>
+        <v>1.116939425468445</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -9059,7 +9059,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D546">
-        <v>4.440277099609375</v>
+        <v>4.308159351348877</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -9073,7 +9073,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D547">
-        <v>2.264771938323975</v>
+        <v>2.069836139678955</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -9087,7 +9087,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D548">
-        <v>4.725138664245605</v>
+        <v>3.38185977935791</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -9101,7 +9101,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D549">
-        <v>3.811185836791992</v>
+        <v>2.005992412567139</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -9115,7 +9115,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D550">
-        <v>5.637164115905762</v>
+        <v>5.574586391448975</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -9129,7 +9129,7 @@
         <v>17.20000076293945</v>
       </c>
       <c r="D551">
-        <v>18.77120208740234</v>
+        <v>16.37526512145996</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -9143,7 +9143,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D552">
-        <v>4.287155151367188</v>
+        <v>3.882501602172852</v>
       </c>
     </row>
   </sheetData>
